--- a/artfynd/A 42202-2025 artfynd.xlsx
+++ b/artfynd/A 42202-2025 artfynd.xlsx
@@ -898,7 +898,7 @@
         <v>132433102</v>
       </c>
       <c r="B4" t="n">
-        <v>83161</v>
+        <v>83163</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -995,7 +995,7 @@
         <v>132433103</v>
       </c>
       <c r="B5" t="n">
-        <v>79315</v>
+        <v>79317</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1202,7 +1202,7 @@
         <v>132433101</v>
       </c>
       <c r="B7" t="n">
-        <v>79315</v>
+        <v>79317</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 42202-2025 artfynd.xlsx
+++ b/artfynd/A 42202-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>132433104</v>
       </c>
       <c r="B2" t="n">
-        <v>57948</v>
+        <v>57949</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -788,7 +788,7 @@
         <v>132433100</v>
       </c>
       <c r="B3" t="n">
-        <v>57948</v>
+        <v>57949</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -898,7 +898,7 @@
         <v>132433102</v>
       </c>
       <c r="B4" t="n">
-        <v>83163</v>
+        <v>83165</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -995,7 +995,7 @@
         <v>132433103</v>
       </c>
       <c r="B5" t="n">
-        <v>79317</v>
+        <v>79319</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1092,7 +1092,7 @@
         <v>132433107</v>
       </c>
       <c r="B6" t="n">
-        <v>57948</v>
+        <v>57949</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1202,7 +1202,7 @@
         <v>132433101</v>
       </c>
       <c r="B7" t="n">
-        <v>79317</v>
+        <v>79319</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1299,7 +1299,7 @@
         <v>132433108</v>
       </c>
       <c r="B8" t="n">
-        <v>57948</v>
+        <v>57949</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1409,7 +1409,7 @@
         <v>132433099</v>
       </c>
       <c r="B9" t="n">
-        <v>57948</v>
+        <v>57949</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1519,7 +1519,7 @@
         <v>132433105</v>
       </c>
       <c r="B10" t="n">
-        <v>57948</v>
+        <v>57949</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 42202-2025 artfynd.xlsx
+++ b/artfynd/A 42202-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>132433104</v>
       </c>
       <c r="B2" t="n">
-        <v>57949</v>
+        <v>57953</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -788,7 +788,7 @@
         <v>132433100</v>
       </c>
       <c r="B3" t="n">
-        <v>57949</v>
+        <v>57953</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -898,7 +898,7 @@
         <v>132433102</v>
       </c>
       <c r="B4" t="n">
-        <v>83165</v>
+        <v>83173</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -995,7 +995,7 @@
         <v>132433103</v>
       </c>
       <c r="B5" t="n">
-        <v>79319</v>
+        <v>79327</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1092,7 +1092,7 @@
         <v>132433107</v>
       </c>
       <c r="B6" t="n">
-        <v>57949</v>
+        <v>57953</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1202,7 +1202,7 @@
         <v>132433101</v>
       </c>
       <c r="B7" t="n">
-        <v>79319</v>
+        <v>79327</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1299,7 +1299,7 @@
         <v>132433108</v>
       </c>
       <c r="B8" t="n">
-        <v>57949</v>
+        <v>57953</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1409,7 +1409,7 @@
         <v>132433099</v>
       </c>
       <c r="B9" t="n">
-        <v>57949</v>
+        <v>57953</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1519,7 +1519,7 @@
         <v>132433105</v>
       </c>
       <c r="B10" t="n">
-        <v>57949</v>
+        <v>57953</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 42202-2025 artfynd.xlsx
+++ b/artfynd/A 42202-2025 artfynd.xlsx
@@ -1199,10 +1199,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>132433101</v>
+        <v>132433108</v>
       </c>
       <c r="B7" t="n">
-        <v>79327</v>
+        <v>57953</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1210,37 +1210,45 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Burtjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>591510</v>
+        <v>591389</v>
       </c>
       <c r="R7" t="n">
-        <v>6965836</v>
+        <v>6965829</v>
       </c>
       <c r="S7" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1270,6 +1278,11 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2026-04-13</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Färska ringhack på gran</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1296,10 +1309,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>132433108</v>
+        <v>132433101</v>
       </c>
       <c r="B8" t="n">
-        <v>57953</v>
+        <v>79327</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1307,45 +1320,37 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Burtjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>591389</v>
+        <v>591510</v>
       </c>
       <c r="R8" t="n">
-        <v>6965829</v>
+        <v>6965836</v>
       </c>
       <c r="S8" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1375,11 +1380,6 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2026-04-13</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Färska ringhack på gran</t>
         </is>
       </c>
       <c r="AD8" t="b">

--- a/artfynd/A 42202-2025 artfynd.xlsx
+++ b/artfynd/A 42202-2025 artfynd.xlsx
@@ -1199,10 +1199,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>132433108</v>
+        <v>132433101</v>
       </c>
       <c r="B7" t="n">
-        <v>57953</v>
+        <v>79327</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1210,45 +1210,37 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Burtjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>591389</v>
+        <v>591510</v>
       </c>
       <c r="R7" t="n">
-        <v>6965829</v>
+        <v>6965836</v>
       </c>
       <c r="S7" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1278,11 +1270,6 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2026-04-13</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Färska ringhack på gran</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1309,10 +1296,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>132433101</v>
+        <v>132433108</v>
       </c>
       <c r="B8" t="n">
-        <v>79327</v>
+        <v>57953</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1320,37 +1307,45 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Burtjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>591510</v>
+        <v>591389</v>
       </c>
       <c r="R8" t="n">
-        <v>6965836</v>
+        <v>6965829</v>
       </c>
       <c r="S8" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1380,6 +1375,11 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2026-04-13</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Färska ringhack på gran</t>
         </is>
       </c>
       <c r="AD8" t="b">

--- a/artfynd/A 42202-2025 artfynd.xlsx
+++ b/artfynd/A 42202-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>132433104</v>
       </c>
       <c r="B2" t="n">
-        <v>57953</v>
+        <v>57954</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -788,7 +788,7 @@
         <v>132433100</v>
       </c>
       <c r="B3" t="n">
-        <v>57953</v>
+        <v>57954</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -898,7 +898,7 @@
         <v>132433102</v>
       </c>
       <c r="B4" t="n">
-        <v>83173</v>
+        <v>83174</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -995,7 +995,7 @@
         <v>132433103</v>
       </c>
       <c r="B5" t="n">
-        <v>79327</v>
+        <v>79328</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1092,7 +1092,7 @@
         <v>132433107</v>
       </c>
       <c r="B6" t="n">
-        <v>57953</v>
+        <v>57954</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1199,10 +1199,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>132433101</v>
+        <v>132433108</v>
       </c>
       <c r="B7" t="n">
-        <v>79327</v>
+        <v>57954</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1210,37 +1210,45 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Burtjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>591510</v>
+        <v>591389</v>
       </c>
       <c r="R7" t="n">
-        <v>6965836</v>
+        <v>6965829</v>
       </c>
       <c r="S7" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1270,6 +1278,11 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2026-04-13</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Färska ringhack på gran</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1296,10 +1309,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>132433108</v>
+        <v>132433101</v>
       </c>
       <c r="B8" t="n">
-        <v>57953</v>
+        <v>79328</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1307,45 +1320,37 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Burtjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>591389</v>
+        <v>591510</v>
       </c>
       <c r="R8" t="n">
-        <v>6965829</v>
+        <v>6965836</v>
       </c>
       <c r="S8" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1375,11 +1380,6 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2026-04-13</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Färska ringhack på gran</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1409,7 +1409,7 @@
         <v>132433099</v>
       </c>
       <c r="B9" t="n">
-        <v>57953</v>
+        <v>57954</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1519,7 +1519,7 @@
         <v>132433105</v>
       </c>
       <c r="B10" t="n">
-        <v>57953</v>
+        <v>57954</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
